--- a/data/credit_bond_all_2026-09-11.xlsx
+++ b/data/credit_bond_all_2026-09-11.xlsx
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ48"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -741,7 +741,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5500/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -1340,7 +1340,7 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26栾川钼业MTN001(科创债)</t>
+          <t>26栾川钼业MTN001</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2176,7 +2176,7 @@
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26深圳国际MTN005</t>
+          <t>26深圳国控MTN005</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3421,7 +3421,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AZ15" s="3"/>
+      <c r="AZ15" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
@@ -4261,7 +4263,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AZ19" s="3"/>
+      <c r="AZ19" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
@@ -4503,7 +4507,9 @@
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+      <c r="H21" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -4527,7 +4533,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4800</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -5571,7 +5577,9 @@
           <t>0.10 ~ 10.00</t>
         </is>
       </c>
-      <c r="H26" s="3"/>
+      <c r="H26" s="4" t="n">
+        <v>1.52</v>
+      </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -5595,7 +5603,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5600/--</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -6408,7 +6416,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26黔源GCKV01</t>
+          <t>26城资01</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6418,21 +6426,21 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>525003.SZ</t>
+          <t>283935.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>4+1</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H30" s="3"/>
@@ -6456,10 +6464,14 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>贵州黔源电力股份有限公司</t>
-        </is>
-      </c>
-      <c r="P30" s="3"/>
+          <t>邹城市城资控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>C 28.54</t>
+        </is>
+      </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -6467,7 +6479,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>09-11 14:00</t>
+          <t>09-11 15:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -6482,31 +6494,31 @@
       </c>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
-      <c r="W30" s="3"/>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="X30" s="3"/>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z30" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>贵州省-贵阳市</t>
+          <t>山东省-济宁市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司绿色项目贷款。</t>
+          <t>本期债券的募集资金不超过3.00亿元(含3.00亿元)，扣除发行费用后，全部用于偿还到期的公司债券本金[23城资07]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>川财证券有限责任公司,中信建投证券股份有限公司</t>
+          <t>德邦证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
@@ -6517,22 +6529,22 @@
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>贵州黔源电力股份有限公司2026年面向专业投资者公开发行碳中和绿色科技创新乡村振兴公司债券(第一期)(生物多样性挂钩)(支持生态文明建设先行区)</t>
+          <t>邹城市城资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
@@ -6562,16 +6574,32 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="AP30" s="3"/>
-      <c r="AQ30" s="3"/>
-      <c r="AR30" s="3"/>
-      <c r="AS30" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -6604,49 +6632,45 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26贵州银行小微债</t>
+          <t>26银桥01</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>09-11 18:00</t>
-        </is>
-      </c>
-      <c r="C31" s="3"/>
+          <t>09-11 17:30</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>246058.SH</t>
+        </is>
+      </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>30.0</v>
+        <v>8.9</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>26贵州银行债01</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>2.92Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.6734</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -6656,12 +6680,12 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>贵州银行股份有限公司</t>
+          <t>昆山银桥控股集团有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.08</t>
+          <t>C- 16.43</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -6671,7 +6695,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>09-11 09:00</t>
+          <t>09-11 15:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -6691,40 +6715,32 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X31" s="3" t="inlineStr">
-        <is>
-          <t>1.66%~1.76%</t>
-        </is>
-      </c>
+      <c r="X31" s="3"/>
       <c r="Y31" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z31" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>贵州省-贵阳市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集的资金将依据适用法律和主管部门的批准,全部用于向小型微型企业发放贷款。</t>
+          <t>本期债券募集资金不超过8.90亿元(含8.90亿元),募集资金在扣除发行费用后仅用于置换偿还25银桥01公司债券本金的自有资金。[25银桥01]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,国泰海通证券股份有限公司,光大证券股份有限公司,申万宏源证券有限公司,国开证券股份有限公司,东方证券股份有限公司,中国邮政储蓄银行股份有限公司,重庆银行股份有限公司,中国国际金融股份有限公司</t>
+          <t>东吴证券股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -6734,12 +6750,12 @@
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>贵州银行股份有限公司2026年小型微型企业贷款专项金融债券(第一期)</t>
+          <t>昆山银桥控股集团有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -6749,14 +6765,10 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2029-09-15</t>
-        </is>
-      </c>
-      <c r="AK31" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-15</t>
+        </is>
+      </c>
+      <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6764,7 +6776,7 @@
       </c>
       <c r="AM31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AN31" s="3" t="inlineStr">
@@ -6774,32 +6786,32 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -6832,45 +6844,45 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26平安银行01</t>
+          <t>26青水01</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>09-11 17:00</t>
-        </is>
-      </c>
-      <c r="C32" s="3"/>
+          <t>09-11 18:00</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>283966.SH</t>
+        </is>
+      </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>50.0</v>
+        <v>5.0</v>
       </c>
       <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>25平安银行科创债01BC</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>2.27Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.5831</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -6880,12 +6892,12 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司</t>
+          <t>青岛水务集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>A+ 81.07</t>
+          <t>D+ 5.46</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -6895,7 +6907,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>09-11 09:30</t>
+          <t>09-11 15:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -6905,70 +6917,74 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t>1.59%~1.69%</t>
-        </is>
-      </c>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X32" s="3"/>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
-        </is>
-      </c>
-      <c r="AC32" s="3"/>
+          <t>本期公司债券募集资金扣除发行费用后,拟将3.00亿元用于偿还即将到期的超短期融资券本金,2.00亿元用于偿还即将到期的银行贷款。[青岛水务集团有限公司2026年度第二期超短期融资券]</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>东方证券股份有限公司,华泰联合证券有限责任公司,中泰证券股份有限公司</t>
+        </is>
+      </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>集体企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司2026年金融债券(第一期)</t>
+          <t>青岛水务集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
-        </is>
-      </c>
-      <c r="AK32" s="3"/>
+          <t>2029-09-15</t>
+        </is>
+      </c>
+      <c r="AK32" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL32" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6976,42 +6992,42 @@
       </c>
       <c r="AM32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AN32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>股份制银行</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7044,55 +7060,45 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26成渝客专MTN001(绿色)</t>
+          <t>26沣西04</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>09-14 18:00</t>
+          <t>09-11 18:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>102683605.IB</t>
+          <t>284010.SH</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>8.5</v>
+      </c>
+      <c r="F33" s="3"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.99</t>
+          <t>2.00 ~ 3.30</t>
         </is>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>24铁道MTN007A</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>3.00Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.5160</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -7102,10 +7108,14 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>成渝铁路客运专线有限责任公司</t>
-        </is>
-      </c>
-      <c r="P33" s="3"/>
+          <t>陕西西咸新区沣西发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>A- 62.95</t>
+        </is>
+      </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -7113,7 +7123,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>09-11 09:00</t>
+          <t>09-11 15:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -7123,124 +7133,136 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
-      <c r="W33" s="3"/>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>8+</t>
+        </is>
+      </c>
       <c r="X33" s="3"/>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>发行人本期拟发行金额10亿元,全部用于绿色产业领域,用于偿还成渝客专项目银行借款本金</t>
+          <t>本次公司债券募集资金扣除发行费用后,拟全部用于偿还或置换区域内到期的公司债券本金</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD33" s="3"/>
+          <t>西部证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr">
+        <is>
+          <t>西安财金投资管理有限公司</t>
+        </is>
+      </c>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>其他分类</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>成渝铁路客运专线有限责任公司2026年度第一期绿色中期票据</t>
+          <t>陕西西咸新区沣西发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2031-09-15</t>
-        </is>
-      </c>
-      <c r="AK33" s="3"/>
+          <t>2031-09-14</t>
+        </is>
+      </c>
+      <c r="AK33" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t/>
         </is>
       </c>
       <c r="AM33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AN33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP33" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-14</t>
         </is>
       </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
@@ -7250,7 +7272,7 @@
       </c>
       <c r="AY33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AZ33" s="3"/>
@@ -7258,12 +7280,12 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26上海银行债02</t>
+          <t>26贵州银行小微债</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>09-11 17:00</t>
+          <t>09-11 18:00</t>
         </is>
       </c>
       <c r="C34" s="3"/>
@@ -7273,41 +7295,49 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>200.0</v>
+        <v>30.0</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>26贵州银行债01</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>2.92Y</t>
+        </is>
+      </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.6734</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6850/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>上海银行股份有限公司</t>
+          <t>贵州银行股份有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>A+ 82.12</t>
+          <t>C+ 34.08</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7332,27 +7362,39 @@
       </c>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
-      <c r="W34" s="3"/>
-      <c r="X34" s="3"/>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>1.66%~1.76%</t>
+        </is>
+      </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z34" s="3"/>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>贵州省-贵阳市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+          <t>本期债券募集的资金将依据适用法律和主管部门的批准,全部用于向小型微型企业发放贷款。</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,国投证券股份有限公司,江苏银行股份有限公司,中信证券股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,中国农业银行股份有限公司,中国银行股份有限公司,中国银河证券股份有限公司,中国建设银行股份有限公司,中国国际金融股份有限公司,东方证券股份有限公司,兴业银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,国泰海通证券股份有限公司,光大证券股份有限公司,申万宏源证券有限公司,国开证券股份有限公司,东方证券股份有限公司,中国邮政储蓄银行股份有限公司,重庆银行股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
@@ -7373,7 +7415,7 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>上海银行股份有限公司2026年第二期金融债券</t>
+          <t>贵州银行股份有限公司2026年小型微型企业贷款专项金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -7398,7 +7440,7 @@
       </c>
       <c r="AM34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AN34" s="3" t="inlineStr">
@@ -7413,7 +7455,7 @@
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
@@ -7466,56 +7508,60 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26苏美达SCP002</t>
+          <t>26平安银行01</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>09-11 18:00</t>
+          <t>09-11 17:00</t>
         </is>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>5.0</v>
+        <v>50.0</v>
       </c>
       <c r="F35" s="3"/>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>1.35 ~ 1.65</t>
-        </is>
-      </c>
+      <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>25平安银行科创债01BC</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>2.27Y</t>
+        </is>
+      </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.5831</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5800/1.5200</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>江苏苏美达集团有限公司</t>
+          <t>平安银行股份有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>A+ 81.07</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -7525,7 +7571,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>09-11 09:00</t>
+          <t>09-11 09:30</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -7542,10 +7588,14 @@
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
-        </is>
-      </c>
-      <c r="X35" s="3"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>1.59%~1.69%</t>
+        </is>
+      </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -7554,28 +7604,24 @@
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额5亿元,用于偿还发行人本部及子公司有息负债。</t>
-        </is>
-      </c>
-      <c r="AC35" s="3" t="inlineStr">
-        <is>
-          <t>中国建设银行股份有限公司,北京银行股份有限公司</t>
-        </is>
-      </c>
+          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AC35" s="3"/>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>集体企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
@@ -7585,7 +7631,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>江苏苏美达集团有限公司2026年度第二期超短期融资券</t>
+          <t>平安银行股份有限公司2026年金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -7595,22 +7641,18 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
-      <c r="AK35" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-14</t>
+        </is>
+      </c>
+      <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t/>
         </is>
       </c>
       <c r="AM35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AN35" s="3" t="inlineStr">
@@ -7620,32 +7662,32 @@
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -7678,58 +7720,68 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26中化股SCP011</t>
+          <t>26成渝客专MTN001(绿色)</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>09-11 18:00</t>
-        </is>
-      </c>
-      <c r="C36" s="3"/>
+          <t>09-14 18:00</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>102683605.IB</t>
+        </is>
+      </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>0.08Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F36" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.27 ~ 1.47</t>
+          <t>1.50 ~ 1.99</t>
         </is>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>24铁道MTN007A</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>3.00Y</t>
+        </is>
+      </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.5160</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6200/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>中国中化股份有限公司</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t>A- 63.68</t>
-        </is>
-      </c>
+          <t>成渝铁路客运专线有限责任公司</t>
+        </is>
+      </c>
+      <c r="P36" s="3"/>
       <c r="Q36" s="3" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -7737,7 +7789,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-11 11:00</t>
+          <t>09-11 09:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -7747,47 +7799,47 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
-      <c r="W36" s="3" t="inlineStr">
-        <is>
-          <t>4+</t>
-        </is>
-      </c>
+      <c r="W36" s="3"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z36" s="3"/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券的发行规模为20亿元,募集资金将用于补充流动资金及偿还有息债务。</t>
+          <t>发行人本期拟发行金额10亿元,全部用于绿色产业领域,用于偿还成渝客专项目银行借款本金</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,广发银行股份有限公司</t>
+          <t>招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>其他分类</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
@@ -7797,7 +7849,7 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>中国中化股份有限公司2026年度第十一期超短期融资券</t>
+          <t>成渝铁路客运专线有限责任公司2026年度第一期绿色中期票据</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -7807,78 +7859,74 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2031-09-15</t>
         </is>
       </c>
       <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="AM36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AN36" s="3" t="inlineStr">
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP36" s="3"/>
+      <c r="AQ36" s="3" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>非盈利性交运服务</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>非盈利性交运服务</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>铁路运输</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX36" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY36" s="3" t="inlineStr">
         <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AO36" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="AQ36" s="3" t="inlineStr">
-        <is>
-          <t>化石能源</t>
-        </is>
-      </c>
-      <c r="AR36" s="3" t="inlineStr">
-        <is>
-          <t>石油石化</t>
-        </is>
-      </c>
-      <c r="AS36" s="3" t="inlineStr">
-        <is>
-          <t>石油化工与贸易</t>
-        </is>
-      </c>
-      <c r="AT36" s="3" t="inlineStr">
-        <is>
-          <t>石油开采</t>
-        </is>
-      </c>
-      <c r="AU36" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV36" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW36" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX36" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AZ36" s="3"/>
@@ -7886,27 +7934,27 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26太原钢铁SCP001</t>
+          <t>26上海银行债02</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>09-11 18:00</t>
+          <t>09-11 17:00</t>
         </is>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>10.0</v>
+        <v>200.0</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.57</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H37" s="3"/>
@@ -7930,12 +7978,12 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>太原钢铁(集团)有限公司</t>
+          <t>上海银行股份有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>D 5.00</t>
+          <t>A+ 82.12</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -7955,16 +8003,12 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
-      <c r="W37" s="3" t="inlineStr">
-        <is>
-          <t>4+</t>
-        </is>
-      </c>
+      <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3" t="inlineStr">
         <is>
@@ -7974,28 +8018,28 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>山西省-太原市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券发行金额10亿元,用于偿还发行人有息债务及补充流动资金。</t>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,中国农业银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,国投证券股份有限公司,江苏银行股份有限公司,中信证券股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,中国农业银行股份有限公司,中国银行股份有限公司,中国银河证券股份有限公司,中国建设银行股份有限公司,中国国际金融股份有限公司,东方证券股份有限公司,兴业银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG37" s="3" t="inlineStr">
@@ -8005,7 +8049,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>太原钢铁(集团)有限公司2026年度第一期超短期融资券</t>
+          <t>上海银行股份有限公司2026年第二期金融债券</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8015,7 +8059,7 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2027-03-13</t>
+          <t>2029-09-15</t>
         </is>
       </c>
       <c r="AK37" s="3" t="inlineStr">
@@ -8025,47 +8069,47 @@
       </c>
       <c r="AL37" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="AM37" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>其他钢铁</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8098,7 +8142,7 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26滨建投MTN006</t>
+          <t>26苏美达SCP002</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8109,7 +8153,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
@@ -8118,7 +8162,7 @@
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.35 ~ 1.65</t>
         </is>
       </c>
       <c r="H38" s="3"/>
@@ -8142,12 +8186,12 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>天津滨海新区建设投资集团有限公司</t>
+          <t>江苏苏美达集团有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.69</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8174,7 +8218,7 @@
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X38" s="3"/>
@@ -8186,28 +8230,28 @@
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>天津市-滨海新区</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据注册规模90亿元，本期中期票据基础发行规模0亿元，发行金额上限5亿元【24滨建投MTN013】</t>
+          <t>本期超短期融资券发行金额5亿元,用于偿还发行人本部及子公司有息负债。</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中信证券股份有限公司</t>
+          <t>中国建设银行股份有限公司,北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG38" s="3" t="inlineStr">
@@ -8217,7 +8261,7 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>天津滨海新区建设投资集团有限公司2026年度第六期中期票据</t>
+          <t>江苏苏美达集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -8227,10 +8271,14 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
-        </is>
-      </c>
-      <c r="AK38" s="3"/>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="AK38" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL38" s="3" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -8248,32 +8296,32 @@
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -8306,7 +8354,7 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26北京一轻SCP003</t>
+          <t>26中化股SCP011</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8317,16 +8365,16 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>0.08Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.27 ~ 1.47</t>
         </is>
       </c>
       <c r="H39" s="3"/>
@@ -8350,12 +8398,12 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>北京一轻控股有限责任公司</t>
+          <t>中国中化股份有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>D+ 10.00</t>
+          <t>A- 63.68</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -8365,7 +8413,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>09-11 09:00</t>
+          <t>09-11 11:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -8382,7 +8430,7 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X39" s="3"/>
@@ -8399,12 +8447,12 @@
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额10亿元,拟全部用于偿还发行人本部到期债券北京一轻控股有限责任公司2026年度第二期超短期融资券。[26北京一轻SCP002]</t>
+          <t>发行人本期超短期融资券的发行规模为20亿元,募集资金将用于补充流动资金及偿还有息债务。</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>北京银行股份有限公司</t>
+          <t>兴业银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
@@ -8415,7 +8463,7 @@
       </c>
       <c r="AF39" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG39" s="3" t="inlineStr">
@@ -8425,7 +8473,7 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>北京一轻控股有限责任公司2026年度第三期超短期融资券</t>
+          <t>中国中化股份有限公司2026年度第十一期超短期融资券</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -8435,7 +8483,7 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AK39" s="3"/>
@@ -8461,27 +8509,27 @@
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>轻工制造</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>综合轻工制造</t>
+          <t>石油石化</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>综合轻工制造</t>
+          <t>石油化工与贸易</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>饮料制造</t>
+          <t>石油开采</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -8514,7 +8562,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26华电K6</t>
+          <t>26太原钢铁SCP001</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -8522,23 +8570,19 @@
           <t>09-11 18:00</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>246055.SH</t>
-        </is>
-      </c>
+      <c r="C40" s="3"/>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.30 ~ 1.57</t>
         </is>
       </c>
       <c r="H40" s="3"/>
@@ -8562,12 +8606,12 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>中国华电集团有限公司</t>
+          <t>太原钢铁(集团)有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>B- 42.24</t>
+          <t>D 5.00</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -8577,7 +8621,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>09-11 16:00</t>
+          <t>09-11 09:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -8594,7 +8638,7 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X40" s="3"/>
@@ -8606,38 +8650,38 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>河北省-保定市</t>
+          <t>山西省-太原市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过20亿元,募集资金拟用于生产性支出,包括偿还有息债务、补充流动资金、项目投资及运营等符合法律法规要求的用途。</t>
+          <t>发行人本期超短期融资券发行金额10亿元,用于偿还发行人有息债务及补充流动资金。</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中国国际金融股份有限公司,招商证券股份有限公司,平安证券股份有限公司,光大证券股份有限公司</t>
+          <t>平安银行股份有限公司,中国农业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>中国华电集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第五期)</t>
+          <t>太原钢铁(集团)有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -8647,13 +8691,17 @@
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
-        </is>
-      </c>
-      <c r="AK40" s="3"/>
+          <t>2027-03-13</t>
+        </is>
+      </c>
+      <c r="AK40" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL40" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AM40" s="3" t="inlineStr">
@@ -8673,27 +8721,27 @@
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>其他钢铁</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -8726,7 +8774,7 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26余创01</t>
+          <t>26滨建投MTN006</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -8734,23 +8782,19 @@
           <t>09-11 18:00</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>283845.SH</t>
-        </is>
-      </c>
+      <c r="C41" s="3"/>
       <c r="D41" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>18.0</v>
+        <v>5.0</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H41" s="3"/>
@@ -8774,10 +8818,14 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>杭州余杭创新产业发展运营有限公司</t>
-        </is>
-      </c>
-      <c r="P41" s="3"/>
+          <t>天津滨海新区建设投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>C+ 33.69</t>
+        </is>
+      </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -8785,7 +8833,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>09-11 15:00</t>
+          <t>09-11 09:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -8795,100 +8843,120 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
-      <c r="W41" s="3"/>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
       <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>天津市-滨海新区</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟募集资金规模不超过18亿元(含18亿元),本期债券的募集资金扣除发行费用后,拟用于偿还有息负债等</t>
+          <t>本次中期票据注册规模90亿元，本期中期票据基础发行规模0亿元，发行金额上限5亿元【24滨建投MTN013】</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,平安证券股份有限公司</t>
+          <t>中信银行股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
         <is>
-          <t>其他分类</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG41" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>杭州余杭创新产业发展运营有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>天津滨海新区建设投资集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2029-09-15</t>
-        </is>
-      </c>
-      <c r="AK41" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2029-09-14</t>
+        </is>
+      </c>
+      <c r="AK41" s="3"/>
       <c r="AL41" s="3" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM41" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AO41" s="3" t="inlineStr">
-        <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="AP41" s="3"/>
-      <c r="AQ41" s="3"/>
-      <c r="AR41" s="3"/>
-      <c r="AS41" s="3"/>
-      <c r="AT41" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU41" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV41" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -8909,12 +8977,14 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AZ41" s="3"/>
+      <c r="AZ41" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26延长K8</t>
+          <t>26北京一轻SCP003</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -8922,23 +8992,19 @@
           <t>09-11 18:00</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>246076.SH</t>
-        </is>
-      </c>
+      <c r="C42" s="3"/>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>45.0</v>
+        <v>10.0</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.00</t>
+          <t>1.30 ~ 1.70</t>
         </is>
       </c>
       <c r="H42" s="3"/>
@@ -8962,12 +9028,12 @@
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>陕西延长石油(集团)有限责任公司</t>
+          <t>北京一轻控股有限责任公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>B+ 55.34</t>
+          <t>D+ 10.00</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -8977,7 +9043,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>09-11 15:00</t>
+          <t>09-11 09:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -8994,7 +9060,7 @@
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X42" s="3"/>
@@ -9006,23 +9072,23 @@
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>陕西省-延安市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过45亿元,募集资金扣除发行费用后,拟用于偿还有息债务和补充流动资金;其中30亿元拟用于偿还有息债务,剩余15亿元拟用于补充日常经营流动资金</t>
+          <t>本期超短期融资券发行金额10亿元,拟全部用于偿还发行人本部到期债券北京一轻控股有限责任公司2026年度第二期超短期融资券。[26北京一轻SCP002]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,国投证券股份有限公司,中国国际金融股份有限公司,东方证券股份有限公司,中信证券股份有限公司,招商证券股份有限公司,申万宏源证券有限公司,东吴证券股份有限公司,中国银河证券股份有限公司,广发证券股份有限公司</t>
+          <t>北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
@@ -9032,12 +9098,12 @@
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>陕西延长石油(集团)有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第八期)</t>
+          <t>北京一轻控股有限责任公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
@@ -9047,17 +9113,13 @@
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2031-09-14</t>
-        </is>
-      </c>
-      <c r="AK42" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="AK42" s="3"/>
       <c r="AL42" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AM42" s="3" t="inlineStr">
@@ -9077,27 +9139,27 @@
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>轻工制造</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>石油石化</t>
+          <t>综合轻工制造</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>其他石油石化</t>
+          <t>综合轻工制造</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>石油开采</t>
+          <t>饮料制造</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">
@@ -9130,7 +9192,7 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26路科01</t>
+          <t>26华电K6</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -9140,21 +9202,21 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>283958.SH</t>
+          <t>246055.SH</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H43" s="3"/>
@@ -9178,12 +9240,12 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>台州路桥科创集团有限公司</t>
+          <t>中国华电集团有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>D- 3.00</t>
+          <t>B- 42.24</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -9203,43 +9265,39 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="U43" s="3"/>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X43" s="3"/>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>浙江省-台州市</t>
+          <t>河北省-保定市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟全部用于偿还到期回售的公司债券本金[23路桥01]</t>
+          <t>本期债券发行规模为不超过20亿元,募集资金拟用于生产性支出,包括偿还有息债务、补充流动资金、项目投资及运营等符合法律法规要求的用途。</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD43" s="3" t="inlineStr">
-        <is>
-          <t>台州市路桥公共资产投资管理集团有限公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司,中国国际金融股份有限公司,招商证券股份有限公司,平安证券股份有限公司,光大证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -9247,7 +9305,7 @@
       </c>
       <c r="AF43" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG43" s="3" t="inlineStr">
@@ -9257,17 +9315,17 @@
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>台州路桥科创集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>中国华电集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2031-09-15</t>
+          <t>2029-09-14</t>
         </is>
       </c>
       <c r="AK43" s="3"/>
@@ -9283,52 +9341,52 @@
       </c>
       <c r="AN43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>火电</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
         <is>
-          <t>2029-09-15</t>
+          <t/>
         </is>
       </c>
       <c r="AV43" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW43" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX43" s="3" t="inlineStr">
@@ -9346,7 +9404,7 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26淄博05</t>
+          <t>26余创01</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -9356,21 +9414,21 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>283967.SH</t>
+          <t>283845.SH</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>5.0</v>
+        <v>18.0</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H44" s="3"/>
@@ -9394,14 +9452,10 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>淄博市城市资产运营集团有限公司</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t>B- 36.53</t>
-        </is>
-      </c>
+          <t>杭州余杭创新产业发展运营有限公司</t>
+        </is>
+      </c>
+      <c r="P44" s="3"/>
       <c r="Q44" s="3" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -9409,7 +9463,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>09-11 16:00</t>
+          <t>09-11 15:00</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -9424,31 +9478,23 @@
       </c>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t>5-</t>
-        </is>
-      </c>
+      <c r="W44" s="3"/>
       <c r="X44" s="3"/>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>山东省-淄博市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过人民币5亿元(含5亿元),扣除发行费用后拟用于偿还发行人到期公司债券本金[23 淄博05]</t>
+          <t>本期债券拟募集资金规模不超过18亿元(含18亿元),本期债券的募集资金扣除发行费用后,拟用于偿还有息负债等</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,长城证券股份有限公司,兴业证券股份有限公司,德邦证券股份有限公司,万联证券股份有限公司,华金证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
@@ -9459,7 +9505,7 @@
       </c>
       <c r="AF44" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>其他分类</t>
         </is>
       </c>
       <c r="AG44" s="3" t="inlineStr">
@@ -9469,7 +9515,7 @@
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>淄博市城市资产运营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>杭州余杭创新产业发展运营有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -9479,10 +9525,14 @@
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2031-09-15</t>
-        </is>
-      </c>
-      <c r="AK44" s="3"/>
+          <t>2029-09-15</t>
+        </is>
+      </c>
+      <c r="AK44" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL44" s="3" t="inlineStr">
         <is>
           <t/>
@@ -9500,32 +9550,16 @@
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ44" s="3" t="inlineStr">
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="AP44" s="3"/>
+      <c r="AQ44" s="3"/>
+      <c r="AR44" s="3"/>
+      <c r="AS44" s="3"/>
+      <c r="AT44" s="3" t="inlineStr">
         <is>
           <t>综合</t>
-        </is>
-      </c>
-      <c r="AR44" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS44" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT44" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
         </is>
       </c>
       <c r="AU44" s="3" t="inlineStr">
@@ -9558,31 +9592,31 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26惠州产投01</t>
+          <t>26延长K8</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>09-11 17:00</t>
+          <t>09-11 18:00</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>520461.SZ</t>
+          <t>246076.SH</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>4.0</v>
+        <v>45.0</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 2.00</t>
         </is>
       </c>
       <c r="H45" s="3"/>
@@ -9606,12 +9640,12 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>惠州市产业投资集团有限公司</t>
+          <t>陕西延长石油(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>B- 39.13</t>
+          <t>B+ 55.34</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -9631,36 +9665,36 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X45" s="3"/>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>广东省-惠州市</t>
+          <t>陕西省-延安市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还有息债务。</t>
+          <t>本期债券发行规模为不超过45亿元,募集资金扣除发行费用后,拟用于偿还有息债务和补充流动资金;其中30亿元拟用于偿还有息债务,剩余15亿元拟用于补充日常经营流动资金</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>华金证券股份有限公司,广发证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,国投证券股份有限公司,中国国际金融股份有限公司,东方证券股份有限公司,中信证券股份有限公司,招商证券股份有限公司,申万宏源证券有限公司,东吴证券股份有限公司,中国银河证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
@@ -9676,25 +9710,29 @@
       </c>
       <c r="AG45" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>惠州市产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>陕西延长石油(集团)有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第八期)</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2031-09-15</t>
-        </is>
-      </c>
-      <c r="AK45" s="3"/>
+          <t>2031-09-14</t>
+        </is>
+      </c>
+      <c r="AK45" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL45" s="3" t="inlineStr">
         <is>
           <t/>
@@ -9707,42 +9745,42 @@
       </c>
       <c r="AN45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>石油石化</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>其他石油石化</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>石油开采</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
         <is>
-          <t>2029-09-15</t>
+          <t/>
         </is>
       </c>
       <c r="AV45" s="3" t="inlineStr">
@@ -9752,7 +9790,7 @@
       </c>
       <c r="AW45" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX45" s="3" t="inlineStr">
@@ -9770,7 +9808,7 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26岭南01</t>
+          <t>26路科01</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -9780,21 +9818,21 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>525006.SZ</t>
+          <t>283958.SH</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H46" s="3"/>
@@ -9818,7 +9856,7 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>广州岭南商旅投资集团有限公司</t>
+          <t>台州路桥科创集团有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
@@ -9833,7 +9871,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>09-11 15:00</t>
+          <t>09-11 16:00</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
@@ -9850,32 +9888,36 @@
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X46" s="3"/>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>浙江省-台州市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,将全部用于偿还有息债务</t>
+          <t>本期债券募集资金拟全部用于偿还到期回售的公司债券本金[23路桥01]</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD46" s="3"/>
+          <t>中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr">
+        <is>
+          <t>台州市路桥公共资产投资管理集团有限公司</t>
+        </is>
+      </c>
       <c r="AE46" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -9888,87 +9930,83 @@
       </c>
       <c r="AG46" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>广州岭南商旅投资集团有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>台州路桥科创集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
+          <t>2031-09-15</t>
+        </is>
+      </c>
+      <c r="AK46" s="3"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
           <t>2029-09-15</t>
         </is>
       </c>
-      <c r="AK46" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
-      <c r="AL46" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM46" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AO46" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ46" s="3" t="inlineStr">
-        <is>
-          <t>贸易零售</t>
-        </is>
-      </c>
-      <c r="AR46" s="3" t="inlineStr">
-        <is>
-          <t>其他零售</t>
-        </is>
-      </c>
-      <c r="AS46" s="3" t="inlineStr">
-        <is>
-          <t>其他零售</t>
-        </is>
-      </c>
-      <c r="AT46" s="3" t="inlineStr">
-        <is>
-          <t>一般零售</t>
-        </is>
-      </c>
-      <c r="AU46" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV46" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW46" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX46" s="3" t="inlineStr">
@@ -9986,7 +10024,7 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26格力01</t>
+          <t>26淄博05</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -9996,21 +10034,21 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>525002.SZ</t>
+          <t>283967.SH</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H47" s="3"/>
@@ -10034,12 +10072,12 @@
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>珠海格力集团有限公司</t>
+          <t>淄博市城市资产运营集团有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.90</t>
+          <t>B- 36.53</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -10049,7 +10087,7 @@
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>09-11 15:00</t>
+          <t>09-11 16:00</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
@@ -10066,7 +10104,7 @@
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X47" s="3"/>
@@ -10078,17 +10116,17 @@
       <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>广东省-珠海市</t>
+          <t>山东省-淄博市</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行等相关费用后,拟将10亿元用于偿还有息债务</t>
+          <t>本期债券发行规模为不超过人民币5亿元(含5亿元),扣除发行费用后拟用于偿还发行人到期公司债券本金[23 淄博05]</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,广发证券股份有限公司,中国银河证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,长城证券股份有限公司,兴业证券股份有限公司,德邦证券股份有限公司,万联证券股份有限公司,华金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
@@ -10104,29 +10142,25 @@
       </c>
       <c r="AG47" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>珠海格力集团有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>淄博市城市资产运营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ47" s="3" t="inlineStr">
         <is>
-          <t>2029-09-15</t>
-        </is>
-      </c>
-      <c r="AK47" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-15</t>
+        </is>
+      </c>
+      <c r="AK47" s="3"/>
       <c r="AL47" s="3" t="inlineStr">
         <is>
           <t/>
@@ -10149,7 +10183,7 @@
       </c>
       <c r="AP47" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ47" s="3" t="inlineStr">
@@ -10159,17 +10193,17 @@
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
         <is>
-          <t>装修装饰</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU47" s="3" t="inlineStr">
@@ -10202,31 +10236,31 @@
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26云南能投GCV01</t>
+          <t>26惠州产投01</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>09-11 18:00</t>
+          <t>09-11 17:00</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>525007.SZ</t>
+          <t>520461.SZ</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H48" s="3"/>
@@ -10250,10 +10284,14 @@
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>云南能源投资股份有限公司</t>
-        </is>
-      </c>
-      <c r="P48" s="3"/>
+          <t>惠州市产业投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>B- 39.13</t>
+        </is>
+      </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
           <t>2026-09-11</t>
@@ -10276,27 +10314,31 @@
       </c>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
-      <c r="W48" s="3"/>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
       <c r="X48" s="3"/>
       <c r="Y48" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>云南省-昆明市</t>
+          <t>广东省-惠州市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将15,750.00万元用于偿还碳中和绿色项目有息债务;不超过34,250.00万元用于置换债券发行前12个月内对子公司的自有资金投入,穿透后专项用于绿色项目建设</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,中信证券股份有限公司</t>
+          <t>华金证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
@@ -10317,79 +10359,1767 @@
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
+          <t>惠州市产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-15</t>
+        </is>
+      </c>
+      <c r="AK48" s="3"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>2029-09-15</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AZ48" s="3"/>
+    </row>
+    <row r="49" customHeight="true" ht="18.0">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>26岭南01</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>09-11 18:00</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>525006.SZ</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>广州岭南商旅投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>D- 3.00</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>09-11 15:00</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="U49" s="3"/>
+      <c r="V49" s="3"/>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X49" s="3"/>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z49" s="3"/>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>广东省-广州市</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金扣除发行费用后,将全部用于偿还有息债务</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>广发证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD49" s="3"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr">
+        <is>
+          <t>广州岭南商旅投资集团有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr">
+        <is>
+          <t>2029-09-15</t>
+        </is>
+      </c>
+      <c r="AK49" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr">
+        <is>
+          <t>贸易零售</t>
+        </is>
+      </c>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>其他零售</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>其他零售</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>一般零售</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX49" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AZ49" s="3"/>
+    </row>
+    <row r="50" customHeight="true" ht="18.0">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>26格力01</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>09-11 18:00</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>525002.SZ</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>1.40 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>珠海格力集团有限公司</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>C+ 31.90</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>09-11 15:00</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="U50" s="3"/>
+      <c r="V50" s="3"/>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X50" s="3"/>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z50" s="3"/>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>广东省-珠海市</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>本期公司债券募集资金扣除发行等相关费用后,拟将10亿元用于偿还有息债务</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>中国国际金融股份有限公司,广发证券股份有限公司,中国银河证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD50" s="3"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr">
+        <is>
+          <t>珠海格力集团有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="AI50" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ50" s="3" t="inlineStr">
+        <is>
+          <t>2029-09-15</t>
+        </is>
+      </c>
+      <c r="AK50" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>装修装饰</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX50" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AZ50" s="3"/>
+    </row>
+    <row r="51" customHeight="true" ht="18.0">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>26云南能投GCV01</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>09-11 18:00</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>525007.SZ</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>云南能源投资股份有限公司</t>
+        </is>
+      </c>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>09-11 15:00</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T51" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="U51" s="3"/>
+      <c r="V51" s="3"/>
+      <c r="W51" s="3"/>
+      <c r="X51" s="3"/>
+      <c r="Y51" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z51" s="3"/>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>云南省-昆明市</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金扣除发行费用后,拟将15,750.00万元用于偿还碳中和绿色项目有息债务;不超过34,250.00万元用于置换债券发行前12个月内对子公司的自有资金投入,穿透后专项用于绿色项目建设</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>广发证券股份有限公司,中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD51" s="3"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr">
+        <is>
           <t>云南能源投资股份有限公司2026年面向专业投资者公开发行碳中和绿色乡村振兴公司债券(第一期)</t>
         </is>
       </c>
-      <c r="AI48" s="3" t="inlineStr">
+      <c r="AI51" s="3" t="inlineStr">
         <is>
           <t>公募</t>
         </is>
       </c>
-      <c r="AJ48" s="3" t="inlineStr">
+      <c r="AJ51" s="3" t="inlineStr">
         <is>
           <t>2029-09-15</t>
         </is>
       </c>
-      <c r="AK48" s="3" t="inlineStr">
+      <c r="AK51" s="3" t="inlineStr">
         <is>
           <t>休2</t>
         </is>
       </c>
-      <c r="AL48" s="3" t="inlineStr">
+      <c r="AL51" s="3" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="AM48" s="3" t="inlineStr">
+      <c r="AM51" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
+      <c r="AN51" s="3" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="AO48" s="3" t="inlineStr">
+      <c r="AO51" s="3" t="inlineStr">
         <is>
           <t>其它</t>
         </is>
       </c>
-      <c r="AP48" s="3"/>
-      <c r="AQ48" s="3"/>
-      <c r="AR48" s="3"/>
-      <c r="AS48" s="3"/>
-      <c r="AT48" s="3" t="inlineStr">
+      <c r="AP51" s="3"/>
+      <c r="AQ51" s="3"/>
+      <c r="AR51" s="3"/>
+      <c r="AS51" s="3"/>
+      <c r="AT51" s="3" t="inlineStr">
         <is>
           <t>电力</t>
         </is>
       </c>
-      <c r="AU48" s="3" t="inlineStr">
+      <c r="AU51" s="3" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="AV48" s="3" t="inlineStr">
+      <c r="AV51" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
         </is>
       </c>
-      <c r="AW48" s="3" t="inlineStr">
+      <c r="AW51" s="3" t="inlineStr">
         <is>
           <t>不含权</t>
         </is>
       </c>
-      <c r="AX48" s="3" t="inlineStr">
+      <c r="AX51" s="3" t="inlineStr">
         <is>
           <t>普通债权</t>
         </is>
       </c>
-      <c r="AY48" s="3" t="inlineStr">
+      <c r="AY51" s="3" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AZ48" s="3"/>
+      <c r="AZ51" s="3"/>
+    </row>
+    <row r="52" customHeight="true" ht="18.0">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>26乐山02</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>09-11 18:00</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>283993.SH</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>乐山城市更新集团有限公司</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>E 0.00</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>09-11 16:00</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T52" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="U52" s="3"/>
+      <c r="V52" s="3"/>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X52" s="3"/>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z52" s="3"/>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>四川省-乐山市</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金5亿元扣除发行费用后,拟用于置换偿还到期公司债券本金的自有资金[23乐山02]</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD52" s="3"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr">
+        <is>
+          <t>乐山城市更新集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-15</t>
+        </is>
+      </c>
+      <c r="AK52" s="3"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ52" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX52" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY52" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AZ52" s="3"/>
+    </row>
+    <row r="53" customHeight="true" ht="18.0">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>26粤港03</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>09-11 18:00</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>246080.SH</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>广州港股份有限公司</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>C- 13.91</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>09-11 15:00</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T53" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="U53" s="3"/>
+      <c r="V53" s="3"/>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X53" s="3"/>
+      <c r="Y53" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z53" s="3"/>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>广东省-广州市</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>本期公司债券发行总额为不超过10亿元,募集资金扣除发行费用后拟全部用于偿还有息债务。</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD53" s="3"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr">
+        <is>
+          <t>广州港股份有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+        </is>
+      </c>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr">
+        <is>
+          <t>2029-09-15</t>
+        </is>
+      </c>
+      <c r="AK53" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>港口</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX53" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY53" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AZ53" s="3"/>
+    </row>
+    <row r="54" customHeight="true" ht="18.0">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>26国新K3</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>09-11 18:00</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>246086.SH</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>中国国新控股有限责任公司</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>B+ 58.29</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>09-11 16:00</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T54" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="U54" s="3"/>
+      <c r="V54" s="3"/>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X54" s="3"/>
+      <c r="Y54" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z54" s="3"/>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>本期债券发行金额为不超过20亿元（含），募集资金扣除发行费用后,拟全部用于偿还投资国家石油天然气 管网集团有限公司的并购贷款。</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,招商证券股份有限公司,国新证券股份有限公司,申万宏源证券有限公司,东方证券股份有限公司,长江证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD54" s="3"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr">
+        <is>
+          <t>中央国有企业</t>
+        </is>
+      </c>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr">
+        <is>
+          <t>中国国新控股有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="AI54" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ54" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-15</t>
+        </is>
+      </c>
+      <c r="AK54" s="3"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ54" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX54" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY54" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AZ54" s="3"/>
+    </row>
+    <row r="55" customHeight="true" ht="18.0">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>26锦汇01</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>09-11 18:00</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>284000.SH</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>1.55 ~ 2.55</t>
+        </is>
+      </c>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>江苏锦汇集团有限公司</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>D- 2.96</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>09-11 15:00</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>江苏省-南通市</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>本期公司债券募集资金拟全部用于偿还回售或到期公司债券本金[23锦汇01]</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>申万宏源证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr">
+        <is>
+          <t>启东国有资产投资控股有限公司</t>
+        </is>
+      </c>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr">
+        <is>
+          <t>江苏锦汇集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-15</t>
+        </is>
+      </c>
+      <c r="AK55" s="3"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ55" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX55" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AZ55" s="3"/>
+    </row>
+    <row r="56" customHeight="true" ht="18.0">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>26黔源GCKV01</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>09-11 18:00</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>525003.SZ</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>贵州黔源电力股份有限公司</t>
+        </is>
+      </c>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>09-11 14:00</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T56" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>贵州省-贵阳市</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="inlineStr">
+        <is>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司绿色项目贷款。</t>
+        </is>
+      </c>
+      <c r="AC56" s="3" t="inlineStr">
+        <is>
+          <t>川财证券有限责任公司,中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF56" s="3" t="inlineStr">
+        <is>
+          <t>国有企业</t>
+        </is>
+      </c>
+      <c r="AG56" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="inlineStr">
+        <is>
+          <t>贵州黔源电力股份有限公司2026年面向专业投资者公开发行碳中和绿色科技创新乡村振兴公司债券(第一期)(生物多样性挂钩)(支持生态文明建设先行区)</t>
+        </is>
+      </c>
+      <c r="AI56" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ56" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-14</t>
+        </is>
+      </c>
+      <c r="AK56" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AL56" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>其它</t>
+        </is>
+      </c>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
+      <c r="AR56" s="3"/>
+      <c r="AS56" s="3"/>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX56" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY56" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AZ56" s="3"/>
     </row>
   </sheetData>
   <mergeCells>
